--- a/合同全生命周期管理系统-项目管理套件/07_质量测试与验收/质量测试与验收-20260918-V5.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/07_质量测试与验收/质量测试与验收-20260918-V5.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="12660" firstSheet="4" activeTab="9"/>
+    <workbookView windowWidth="28260" windowHeight="12660"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="11" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="UAT验收" sheetId="8" r:id="rId9"/>
     <sheet name="_数据接口" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,12 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="612">
   <si>
     <t>质量测试与验收-20260918-V5 使用说明</t>
   </si>
   <si>
-    <t>管理质量目标、测试场景、缺陷、需求覆盖、数据质量、UAT和交付验收。</t>
+    <t>管理质量目标、测试场景、缺陷、需求覆盖、数据质量、UAT和交付验收；交付物清单单独维护于《验收交付物》工作簿。</t>
   </si>
   <si>
     <t>项目</t>
@@ -89,7 +89,7 @@
     <t>核验集成、数据迁移和UAT证据</t>
   </si>
   <si>
-    <t>汇总交付物并完成验收签署</t>
+    <t>在《验收交付物》工作簿维护交付物清单，完成评审与验收签署</t>
   </si>
   <si>
     <t>工作表导航</t>
@@ -150,12 +150,6 @@
   </si>
   <si>
     <t>管理业务验收场景和签署。</t>
-  </si>
-  <si>
-    <t>交付物台账</t>
-  </si>
-  <si>
-    <t>跟踪交付物版本、评审和验收。</t>
   </si>
   <si>
     <t>_数据接口</t>
@@ -2002,12 +1996,6 @@
   </si>
   <si>
     <t>../90_项目数据中心/ai_pmo.db</t>
-  </si>
-  <si>
-    <t>管理质量目标、测试场景、缺陷、需求覆盖、数据质量、UAT和交付验收；交付物清单单独维护于《验收交付物》工作簿。</t>
-  </si>
-  <si>
-    <t>在《验收交付物》工作簿维护交付物清单，完成评审与验收签署</t>
   </si>
 </sst>
 </file>
@@ -2998,13 +2986,13 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3525,7 +3513,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:8">
       <c r="A2" s="26" t="s">
-        <v>614</v>
+        <v>1</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -3638,74 +3626,74 @@
       <c r="H10" s="33"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:8">
-      <c r="A11" s="27">
+      <c r="A11" s="34">
         <v>1</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:8">
-      <c r="A12" s="27">
+      <c r="A12" s="35">
         <v>2</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:8">
-      <c r="A13" s="27">
+      <c r="A13" s="35">
         <v>3</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:8">
-      <c r="A14" s="27">
+      <c r="A14" s="35">
         <v>4</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:8">
-      <c r="A15" s="27">
+      <c r="A15" s="35">
         <v>5</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>615</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
+      <c r="B15" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:8">
       <c r="A16" s="27"/>
@@ -3740,13 +3728,13 @@
       <c r="H18" s="33"/>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:8">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="36" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="27"/>
@@ -3888,10 +3876,10 @@
         <v>9</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
@@ -3911,7 +3899,7 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:8">
       <c r="A31" s="31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B31" s="32"/>
       <c r="C31" s="32"/>
@@ -3922,83 +3910,83 @@
       <c r="H31" s="33"/>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:8">
-      <c r="A32" s="35">
+      <c r="A32" s="34">
         <v>1</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:8">
+      <c r="A33" s="35">
+        <v>2</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+    </row>
+    <row r="34" ht="22" customHeight="1" spans="1:8">
+      <c r="A34" s="35">
+        <v>3</v>
+      </c>
+      <c r="B34" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-    </row>
-    <row r="33" ht="22" customHeight="1" spans="1:8">
-      <c r="A33" s="36">
-        <v>2</v>
-      </c>
-      <c r="B33" s="36" t="s">
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+    </row>
+    <row r="35" ht="22" customHeight="1" spans="1:8">
+      <c r="A35" s="35">
+        <v>4</v>
+      </c>
+      <c r="B35" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-    </row>
-    <row r="34" ht="22" customHeight="1" spans="1:8">
-      <c r="A34" s="36">
-        <v>3</v>
-      </c>
-      <c r="B34" s="36" t="s">
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="1:8">
+      <c r="A36" s="35">
+        <v>5</v>
+      </c>
+      <c r="B36" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-    </row>
-    <row r="35" ht="22" customHeight="1" spans="1:8">
-      <c r="A35" s="36">
-        <v>4</v>
-      </c>
-      <c r="B35" s="36" t="s">
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="1:8">
+      <c r="A37" s="35">
+        <v>6</v>
+      </c>
+      <c r="B37" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-    </row>
-    <row r="36" ht="22" customHeight="1" spans="1:8">
-      <c r="A36" s="36">
-        <v>5</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-    </row>
-    <row r="37" ht="22" customHeight="1" spans="1:8">
-      <c r="A37" s="36">
-        <v>6</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="36"/>
+      <c r="C37" s="35"/>
       <c r="D37" s="37"/>
       <c r="E37" s="37"/>
       <c r="F37" s="37"/>
@@ -4020,7 +4008,7 @@
         <v>7</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C39" s="40"/>
       <c r="D39" s="39"/>
@@ -4032,7 +4020,7 @@
     <row r="40" spans="1:8">
       <c r="A40" s="38"/>
       <c r="B40" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C40" s="40"/>
       <c r="D40" s="39"/>
@@ -4044,7 +4032,7 @@
     <row r="41" ht="17" spans="1:8">
       <c r="A41" s="38"/>
       <c r="B41" s="41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C41" s="40"/>
       <c r="D41" s="39"/>
@@ -4056,7 +4044,7 @@
     <row r="42" ht="17" spans="1:8">
       <c r="A42" s="38"/>
       <c r="B42" s="41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C42" s="40"/>
       <c r="D42" s="39"/>
@@ -4068,7 +4056,7 @@
     <row r="43" spans="1:8">
       <c r="A43" s="38"/>
       <c r="B43" s="41" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C43" s="40"/>
       <c r="D43" s="39"/>
@@ -4146,23 +4134,23 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -4170,15 +4158,15 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B5" s="3">
         <v>46282</v>
@@ -4186,7 +4174,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B6" s="2">
         <f>质量总览!A5</f>
@@ -4195,7 +4183,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B7" s="2">
         <f>质量总览!B5</f>
@@ -4204,7 +4192,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B8" s="2">
         <v>10</v>
@@ -4212,7 +4200,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B9" s="2">
         <v>7</v>
@@ -4220,7 +4208,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B10" s="2">
         <f>COUNTIF(质量总览!$A$10:$A$100,"&lt;&gt;")</f>
@@ -4229,7 +4217,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B11" s="2">
         <f>质量总览!C5</f>
@@ -4238,7 +4226,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B12" s="2" t="str">
         <f>质量总览!F5</f>
@@ -4247,7 +4235,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B13" s="3">
         <v>46492</v>
@@ -4255,7 +4243,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B14" s="3">
         <v>46517</v>
@@ -4263,10 +4251,10 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -4291,7 +4279,7 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:6">
       <c r="A1" s="17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4301,27 +4289,27 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="D4" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="E4" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="F4" s="19" t="s">
         <v>59</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4352,7 +4340,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -4362,39 +4350,39 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:6">
       <c r="A9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="D10" s="3">
         <v>46356</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>30</v>
@@ -4402,59 +4390,59 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D11" s="3">
         <v>46387</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D12" s="3">
         <v>46446</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" s="3">
         <v>46456</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>32</v>
@@ -4462,19 +4450,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" s="3">
         <v>46466</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>32</v>
@@ -4482,39 +4470,39 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D15" s="3">
         <v>46492</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" s="3">
         <v>46507</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>34</v>
@@ -4522,19 +4510,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D17" s="3">
         <v>46517</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>36</v>
@@ -4542,42 +4530,42 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D18" s="3">
         <v>46531</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D19" s="3">
         <v>46568</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -4619,293 +4607,293 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8">
       <c r="A4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="E5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="D6" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="G6" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>118</v>
-      </c>
       <c r="H6" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="D7" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="E7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="G7" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>124</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="D8" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="G8" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>129</v>
-      </c>
       <c r="H8" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="D9" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="E9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>132</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>134</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>28</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="D10" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="E10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="G10" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="H10" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="D11" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="E11" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="G11" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>146</v>
-      </c>
       <c r="H11" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="D12" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="G12" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>151</v>
-      </c>
       <c r="H12" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="D13" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>155</v>
-      </c>
       <c r="G13" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="D14" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="G14" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>160</v>
-      </c>
       <c r="H14" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -4946,742 +4934,742 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:11">
       <c r="A4" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="I5" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="K5" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="H6" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="I6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="K6" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="H7" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="H8" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="H9" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="I9" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="K9" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="H10" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="I10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="K10" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="H11" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="I11" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="H12" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="F13" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="H13" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="I13" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="E14" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="H14" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="I14" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="K14" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="F15" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="H15" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="D16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="H16" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>268</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="H17" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="D18" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="H18" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="I18" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="K18" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="D19" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="E19" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="F19" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="H19" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="I19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="K19" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="D20" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="F20" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="H20" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="I20" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="K20" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="D21" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="E21" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="G21" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="H21" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>310</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="D22" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="E22" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="F22" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="G22" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="H22" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="I22" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="K22" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D23" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="E23" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="H23" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="I23" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="K23" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="D24" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="E24" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="G24" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="H24" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="I24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="K24" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -5974,63 +5962,63 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="N4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -8063,7 +8051,7 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:12">
       <c r="A1" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8079,62 +8067,62 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F5" s="13">
         <v>46492</v>
@@ -8142,7 +8130,7 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -8153,19 +8141,19 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F6" s="13">
         <v>46492</v>
@@ -8173,7 +8161,7 @@
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -8184,19 +8172,19 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>374</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F7" s="13">
         <v>46492</v>
@@ -8204,7 +8192,7 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -8215,19 +8203,19 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F8" s="13">
         <v>46492</v>
@@ -8235,7 +8223,7 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -8246,19 +8234,19 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F9" s="13">
         <v>46492</v>
@@ -8266,7 +8254,7 @@
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -8277,19 +8265,19 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F10" s="13">
         <v>46492</v>
@@ -8297,7 +8285,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -8308,19 +8296,19 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F11" s="13">
         <v>46492</v>
@@ -8328,7 +8316,7 @@
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -8339,19 +8327,19 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F12" s="13">
         <v>46492</v>
@@ -8359,7 +8347,7 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -8370,19 +8358,19 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F13" s="13">
         <v>46492</v>
@@ -8390,7 +8378,7 @@
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
@@ -8401,19 +8389,19 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F14" s="13">
         <v>46492</v>
@@ -8421,7 +8409,7 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -8432,19 +8420,19 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>390</v>
-      </c>
       <c r="E15" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F15" s="13">
         <v>46492</v>
@@ -8452,7 +8440,7 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
@@ -8463,19 +8451,19 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F16" s="13">
         <v>46492</v>
@@ -8483,7 +8471,7 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -8494,19 +8482,19 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>396</v>
-      </c>
       <c r="E17" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F17" s="13">
         <v>46492</v>
@@ -8514,7 +8502,7 @@
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
@@ -8525,19 +8513,19 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F18" s="13">
         <v>46492</v>
@@ -8545,7 +8533,7 @@
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
@@ -8556,19 +8544,19 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F19" s="13">
         <v>46492</v>
@@ -8576,7 +8564,7 @@
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -8587,19 +8575,19 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F20" s="13">
         <v>46492</v>
@@ -8607,7 +8595,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -8618,19 +8606,19 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F21" s="13">
         <v>46492</v>
@@ -8638,7 +8626,7 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -8649,19 +8637,19 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F22" s="13">
         <v>46492</v>
@@ -8669,7 +8657,7 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -8680,19 +8668,19 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>411</v>
-      </c>
       <c r="E23" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F23" s="13">
         <v>46492</v>
@@ -8700,7 +8688,7 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
@@ -8711,19 +8699,19 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F24" s="13">
         <v>46492</v>
@@ -8731,7 +8719,7 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
@@ -8742,19 +8730,19 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F25" s="13">
         <v>46492</v>
@@ -8762,7 +8750,7 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
@@ -8773,19 +8761,19 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F26" s="13">
         <v>46492</v>
@@ -8793,7 +8781,7 @@
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
@@ -8804,19 +8792,19 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F27" s="13">
         <v>46492</v>
@@ -8824,7 +8812,7 @@
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
@@ -8835,19 +8823,19 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F28" s="13">
         <v>46492</v>
@@ -8855,7 +8843,7 @@
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
@@ -8897,7 +8885,7 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:14">
       <c r="A1" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8915,68 +8903,68 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:14">
       <c r="A4" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:14">
       <c r="A5" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>435</v>
-      </c>
       <c r="E5" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F5" s="9">
         <v>46433</v>
@@ -8985,40 +8973,40 @@
         <v>46466</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:14">
       <c r="A6" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>443</v>
-      </c>
       <c r="E6" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F6" s="9">
         <v>46433</v>
@@ -9027,40 +9015,40 @@
         <v>46466</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:14">
       <c r="A7" s="8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F7" s="9">
         <v>46433</v>
@@ -9069,40 +9057,40 @@
         <v>46466</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:14">
       <c r="A8" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>451</v>
-      </c>
       <c r="E8" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F8" s="9">
         <v>46433</v>
@@ -9111,40 +9099,40 @@
         <v>46466</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:14">
       <c r="A9" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>455</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F9" s="9">
         <v>46433</v>
@@ -9153,40 +9141,40 @@
         <v>46466</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:14">
       <c r="A10" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>459</v>
-      </c>
       <c r="E10" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F10" s="9">
         <v>46433</v>
@@ -9195,40 +9183,40 @@
         <v>46466</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K10" s="10"/>
       <c r="L10" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:14">
       <c r="A11" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>463</v>
-      </c>
       <c r="E11" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F11" s="9">
         <v>46433</v>
@@ -9237,40 +9225,40 @@
         <v>46466</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K11" s="10"/>
       <c r="L11" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:14">
       <c r="A12" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>442</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>468</v>
-      </c>
       <c r="E12" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F12" s="12">
         <v>46433</v>
@@ -9279,40 +9267,40 @@
         <v>46466</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:14">
       <c r="A13" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>442</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>472</v>
-      </c>
       <c r="E13" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F13" s="12">
         <v>46433</v>
@@ -9321,40 +9309,40 @@
         <v>46466</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:14">
       <c r="A14" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="D14" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>476</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>477</v>
-      </c>
       <c r="E14" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F14" s="12">
         <v>46433</v>
@@ -9363,40 +9351,40 @@
         <v>46466</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:14">
       <c r="A15" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>480</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>476</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>481</v>
-      </c>
       <c r="E15" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F15" s="12">
         <v>46433</v>
@@ -9405,40 +9393,40 @@
         <v>46466</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:14">
       <c r="A16" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>476</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>485</v>
-      </c>
       <c r="E16" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F16" s="12">
         <v>46433</v>
@@ -9447,23 +9435,23 @@
         <v>46466</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -9490,7 +9478,7 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:12">
       <c r="A1" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -9506,68 +9494,68 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="L4" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="E5" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>503</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>505</v>
       </c>
       <c r="H5" s="3">
         <v>46497</v>
@@ -9575,31 +9563,31 @@
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L5" s="7"/>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E6" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>509</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>511</v>
       </c>
       <c r="H6" s="3">
         <v>46497</v>
@@ -9607,31 +9595,31 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L6" s="7"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>515</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>517</v>
       </c>
       <c r="H7" s="3">
         <v>46502</v>
@@ -9639,31 +9627,31 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L7" s="7"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="E8" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>521</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>523</v>
       </c>
       <c r="H8" s="3">
         <v>46502</v>
@@ -9671,31 +9659,31 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L8" s="7"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E9" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>527</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>528</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>529</v>
       </c>
       <c r="H9" s="3">
         <v>46512</v>
@@ -9703,31 +9691,31 @@
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L9" s="7"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="E10" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>533</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>534</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>535</v>
       </c>
       <c r="H10" s="3">
         <v>46512</v>
@@ -9735,7 +9723,7 @@
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L10" s="7"/>
     </row>
@@ -9760,7 +9748,7 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:14">
       <c r="A1" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -9778,410 +9766,410 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:14">
       <c r="A4" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="L4" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="E5" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>549</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>550</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>551</v>
       </c>
       <c r="H5" s="3">
         <v>46495</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N5" s="7"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>557</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>559</v>
       </c>
       <c r="H6" s="3">
         <v>46497</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N6" s="7"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>560</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>561</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>562</v>
       </c>
       <c r="H7" s="3">
         <v>46499</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="E8" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="G8" s="6" t="s">
         <v>565</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>567</v>
       </c>
       <c r="H8" s="3">
         <v>46501</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>569</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>570</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>571</v>
       </c>
       <c r="H9" s="3">
         <v>46503</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N9" s="7"/>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>572</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>573</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>574</v>
       </c>
       <c r="H10" s="3">
         <v>46505</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>578</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>580</v>
       </c>
       <c r="H11" s="3">
         <v>46507</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N11" s="7"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>581</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>583</v>
       </c>
       <c r="H12" s="3">
         <v>46510</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N12" s="7"/>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="G13" s="6" t="s">
         <v>586</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>588</v>
       </c>
       <c r="H13" s="3">
         <v>46512</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="6" t="s">
         <v>591</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>592</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>594</v>
       </c>
       <c r="H14" s="3">
         <v>46515</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N14" s="7"/>
     </row>

--- a/合同全生命周期管理系统-项目管理套件/07_质量测试与验收/质量测试与验收-20260918-V5.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/07_质量测试与验收/质量测试与验收-20260918-V5.xlsx
@@ -1098,7 +1098,7 @@
     <t>核心页面和接口负载测试</t>
   </si>
   <si>
-    <t>测试人员</t>
+    <t>高级测试人员、中级测试人员</t>
   </si>
   <si>
     <t>性能环境和数据准备完成</t>
